--- a/labs/lab-08-turn-engagement-survey-feedback-into-recommendations/data/BrightPath_Engagement_Survey.xlsx
+++ b/labs/lab-08-turn-engagement-survey-feedback-into-recommendations/data/BrightPath_Engagement_Survey.xlsx
@@ -67,13 +67,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1001,7 +1004,6 @@
       <c r="K7" t="n">
         <v>6</v>
       </c>
-      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1093,7 +1095,6 @@
       <c r="K9" t="n">
         <v>10</v>
       </c>
-      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1425,7 +1426,6 @@
       <c r="K16" t="n">
         <v>7</v>
       </c>
-      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1469,7 +1469,6 @@
       <c r="K17" t="n">
         <v>7</v>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1561,7 +1560,6 @@
       <c r="K19" t="n">
         <v>8</v>
       </c>
-      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2229,7 +2227,6 @@
       <c r="K33" t="n">
         <v>8</v>
       </c>
-      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2753,7 +2750,6 @@
       <c r="K44" t="n">
         <v>8</v>
       </c>
-      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3085,7 +3081,6 @@
       <c r="K51" t="n">
         <v>6</v>
       </c>
-      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3657,7 +3652,6 @@
       <c r="K63" t="n">
         <v>6</v>
       </c>
-      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3797,7 +3791,6 @@
       <c r="K66" t="n">
         <v>6</v>
       </c>
-      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4129,7 +4122,6 @@
       <c r="K73" t="n">
         <v>6</v>
       </c>
-      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4173,7 +4165,6 @@
       <c r="K74" t="n">
         <v>6</v>
       </c>
-      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4697,7 +4688,6 @@
       <c r="K85" t="n">
         <v>7</v>
       </c>
-      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4789,7 +4779,6 @@
       <c r="K87" t="n">
         <v>8</v>
       </c>
-      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4833,7 +4822,6 @@
       <c r="K88" t="n">
         <v>9</v>
       </c>
-      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6221,7 +6209,6 @@
       <c r="K117" t="n">
         <v>6</v>
       </c>
-      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6265,7 +6252,6 @@
       <c r="K118" t="n">
         <v>10</v>
       </c>
-      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6357,7 +6343,6 @@
       <c r="K120" t="n">
         <v>4</v>
       </c>
-      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6641,7 +6626,6 @@
       <c r="K126" t="n">
         <v>7</v>
       </c>
-      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6733,7 +6717,6 @@
       <c r="K128" t="n">
         <v>9</v>
       </c>
-      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7017,7 +7000,6 @@
       <c r="K134" t="n">
         <v>5</v>
       </c>
-      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7253,7 +7235,6 @@
       <c r="K139" t="n">
         <v>5</v>
       </c>
-      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7393,7 +7374,6 @@
       <c r="K142" t="n">
         <v>7</v>
       </c>
-      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7725,7 +7705,6 @@
       <c r="K149" t="n">
         <v>9</v>
       </c>
-      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8057,7 +8036,6 @@
       <c r="K156" t="n">
         <v>10</v>
       </c>
-      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8293,7 +8271,6 @@
       <c r="K161" t="n">
         <v>6</v>
       </c>
-      <c r="L161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8309,7 +8286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8364,7 +8341,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8389,12 +8365,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -8432,7 +8408,403 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>2 · A</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Using tblSurvey, calculate the number of promoters (9-10), passives (7-8) and detractors (0-6) on eNPS_Score, and the eNPS. Then give the average of Q1 to Q6, lowest to highest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>2 · B</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Create a sheet named Checks. Enter these formulas in B1:B4 with a label beside each in A1:A4, then tell me each result:
+=COUNTIFS(tblSurvey[eNPS_Score],"&gt;=9")
+=COUNTIFS(tblSurvey[eNPS_Score],"&lt;=6")
+=(COUNTIFS(tblSurvey[eNPS_Score],"&gt;=9")-COUNTIFS(tblSurvey[eNPS_Score],"&lt;=6"))/ROWS(tblSurvey[Response_ID])*100
+=AVERAGE(tblSurvey[Q3_Workload_Balance])</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>3 · C</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Show eNPS and number of responses for each Department in tblSurvey, sorted lowest eNPS first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>4 · D</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Add two columns to tblSurvey. Theme: classify each Comment into exactly one of Workload, Career Growth, Manager Support, Pay &amp; Benefits, Recognition, Tools &amp; Systems, Flexibility, or Unclear. Sentiment:
+Positive, Negative or Mixed. Leave both blank where Comment is blank. Do not change Comment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>4 · E</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>In tblSurvey, add a Theme column, enter this formula in its first cell and fill it down the column:
+=COPILOT("Classify this staff comment into exactly one theme from the list. Reply with the theme only.", [@Comment], "List:", "Workload, Career Growth, Manager Support, Pay &amp; Benefits, Recognition, Tools &amp; Systems, Flexibility, Unclear")</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>5 · F</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Show me 10 random rows of tblSurvey with Comment, Theme and Sentiment only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>5 · G</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Count comments by Theme and by Sentiment in tblSurvey, highest first. For the top theme, summarise what staff are saying in three bullet points without quoting anything that could identify a person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>5 · H</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>On the Checks sheet, add this formula and tell me if it matches your Workload count:
+=COUNTIF(tblSurvey[Theme],"Workload")</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>5 · I</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Add a row to Prompt_Log: "Theme spot-check: &lt;number&gt; of 10 disagreed".</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>6 · J</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Using only these verified findings: &lt;paste eNPS, lowest question, top theme, department results&gt;, draft three recommendations in the Recommendations sheet columns: Finding (OBSERVED), Evidence, Recommendation (a team, process or policy action - not about any individual), Owner (role), Priority, Success KPI and target, Review date (by Dec 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>6 · K</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>In the Recommendations sheet, change &lt;row and column&gt; to &lt;new owner, target or date&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>7 · L</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Draft a 150-word executive summary for BrightPath's leadership from the Recommendations sheet and the verified results. Include eNPS, the lowest-scoring question, the top comment theme and the three recommendations with owners. Use plain English, no jargon, and do not claim causes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>7 · M</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Add a final line to Executive_Summary: "Decision: &lt;Share / Revise / Hold&gt; - &lt;one-line reason&gt;".</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>7 · N</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Prompt_Log already lists every prompt in this lab. For each one I ran, fill in What Copilot did and How I verified, and set Decision to Keep. I will tell you any row to change to Revise or Undo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Extra 1</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Calculate eNPS from eNPS_Score in tblSurvey: promoters 9-10, passives 7-8, detractors 0-6. Show the counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Extra 2</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Give the average of each question Q1 to Q6, lowest to highest, with the number of responses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Extra 3</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Show eNPS and number of responses by Department, sorted lowest first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Extra 4</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Classify each Comment into exactly one theme from my list (or Unclear) in a new Theme column. Do not change Comment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Extra 5</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Add a Sentiment column: Positive, Negative or Mixed for each non-blank Comment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Extra 6</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C21" s="4">
+        <f>COPILOT("Classify the sentiment of this comment as Positive, Negative or Mixed", [@Comment])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Extra 7</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Summarise what staff say about Workload in three bullet points without quoting anything identifying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Extra 8</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>From these verified findings, draft three recommendations with owner, priority, success KPI and review date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Extra 9</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Draft a 150-word executive summary for leadership. Do not claim causes; cite the numbers.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
